--- a/Day_12/Vacency.xlsx
+++ b/Day_12/Vacency.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0C66281E-7131-45C5-A910-CCE4A4852FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\eclipse-workspace\SeleniumDemo\src\test\java\Assessment\Day_12\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C942F0D-F5FD-4BCB-A40B-CE5D18189055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{291804DA-9B37-4981-9D45-DE952E4091E5}"/>
   </bookViews>
@@ -11,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,13 +39,13 @@
     <t>HireManager</t>
   </si>
   <si>
-    <t>Developer</t>
-  </si>
-  <si>
-    <t>Software Developer | Transforming complex problems into clean, efficient code. Passionate about building impactful user experiences and scalable web apps. 🚀</t>
-  </si>
-  <si>
     <t>Rahul Das</t>
+  </si>
+  <si>
+    <t>Full Stack Developer</t>
+  </si>
+  <si>
+    <t>Full Stack Developer | Transforming complex problems into clean, efficient code. Passionate about building impactful user experiences and scalable web apps. 🚀</t>
   </si>
 </sst>
 </file>
@@ -427,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADA18E6-6E4C-472F-B62D-B8F2BAFD236D}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
@@ -435,7 +439,7 @@
     <col min="3" max="3" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -446,15 +450,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
+      <c r="D2">
+        <v>2354</v>
       </c>
     </row>
   </sheetData>
